--- a/regressoes/cdx_us_hy/excel/in/legendas.xlsx
+++ b/regressoes/cdx_us_hy/excel/in/legendas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\assistente_pesquisa\regressao_planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\assistente_pesquisa\pietcon.github.io\regressoes\cdx_us_hy\excel\in\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6E42B6D-22CB-449B-8B18-F88FF329AD1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1B70F8-D1B4-4959-A8F4-317E91C650FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="12210" windowHeight="12885" xr2:uid="{B14FE694-6B0C-4AB5-9869-F41D80E4548F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B14FE694-6B0C-4AB5-9869-F41D80E4548F}"/>
   </bookViews>
   <sheets>
     <sheet name="CAD_Out" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="570">
   <si>
     <t>Emerging Countries Current Account (% EZ GDP)</t>
   </si>
@@ -1745,6 +1745,12 @@
   </si>
   <si>
     <t>Names</t>
+  </si>
+  <si>
+    <t>global_pmi_comp</t>
+  </si>
+  <si>
+    <t>fed_sloos_ci_small_firms_tight_q</t>
   </si>
 </sst>
 </file>
@@ -2165,7 +2171,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:J269"/>
+  <dimension ref="A1:J271"/>
   <sheetFormatPr defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
@@ -3617,7 +3623,7 @@
     </row>
     <row r="93" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C93" s="2" t="s">
-        <v>342</v>
+        <v>568</v>
       </c>
       <c r="D93" t="s">
         <v>204</v>
@@ -3631,7 +3637,7 @@
     </row>
     <row r="94" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C94" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D94" t="s">
         <v>204</v>
@@ -3640,270 +3646,270 @@
         <v>1</v>
       </c>
       <c r="F94" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C95" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D95" t="s">
+        <v>204</v>
+      </c>
+      <c r="E95" t="s">
+        <v>1</v>
+      </c>
+      <c r="F95" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C96" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="D95" t="s">
-        <v>204</v>
-      </c>
-      <c r="E95" t="s">
-        <v>1</v>
-      </c>
-      <c r="F95" t="s">
+      <c r="D96" t="s">
+        <v>204</v>
+      </c>
+      <c r="E96" t="s">
+        <v>1</v>
+      </c>
+      <c r="F96" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="3" t="s">
+    <row r="97" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="B97" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C97" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="D96" t="s">
-        <v>204</v>
-      </c>
-      <c r="E96" t="s">
-        <v>1</v>
-      </c>
-      <c r="F96" t="s">
+      <c r="D97" t="s">
+        <v>204</v>
+      </c>
+      <c r="E97" t="s">
+        <v>1</v>
+      </c>
+      <c r="F97" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="97" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C97" s="2" t="s">
+    <row r="98" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C98" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="D97" t="s">
-        <v>204</v>
-      </c>
-      <c r="E97" t="s">
-        <v>1</v>
-      </c>
-      <c r="F97" t="s">
+      <c r="D98" t="s">
+        <v>204</v>
+      </c>
+      <c r="E98" t="s">
+        <v>1</v>
+      </c>
+      <c r="F98" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="98" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C98" s="2" t="s">
+    <row r="99" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C99" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="D98" t="s">
-        <v>204</v>
-      </c>
-      <c r="E98" t="s">
-        <v>1</v>
-      </c>
-      <c r="F98" t="s">
+      <c r="D99" t="s">
+        <v>204</v>
+      </c>
+      <c r="E99" t="s">
+        <v>1</v>
+      </c>
+      <c r="F99" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="99" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C99" s="2" t="s">
+    <row r="100" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C100" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="D99" t="s">
-        <v>204</v>
-      </c>
-      <c r="E99" t="s">
-        <v>1</v>
-      </c>
-      <c r="F99" t="s">
+      <c r="D100" t="s">
+        <v>204</v>
+      </c>
+      <c r="E100" t="s">
+        <v>1</v>
+      </c>
+      <c r="F100" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="100" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C100" s="2" t="s">
+    <row r="101" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C101" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="D100" t="s">
-        <v>204</v>
-      </c>
-      <c r="E100" t="s">
-        <v>1</v>
-      </c>
-      <c r="F100" t="s">
+      <c r="D101" t="s">
+        <v>204</v>
+      </c>
+      <c r="E101" t="s">
+        <v>1</v>
+      </c>
+      <c r="F101" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="101" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C101" s="2" t="s">
+    <row r="102" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C102" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="D101" t="s">
-        <v>204</v>
-      </c>
-      <c r="E101" t="s">
-        <v>1</v>
-      </c>
-      <c r="F101" t="s">
+      <c r="D102" t="s">
+        <v>204</v>
+      </c>
+      <c r="E102" t="s">
+        <v>1</v>
+      </c>
+      <c r="F102" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="102" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C102" s="2" t="s">
+    <row r="103" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C103" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="D102" t="s">
-        <v>204</v>
-      </c>
-      <c r="E102" t="s">
-        <v>1</v>
-      </c>
-      <c r="F102" t="s">
+      <c r="D103" t="s">
+        <v>204</v>
+      </c>
+      <c r="E103" t="s">
+        <v>1</v>
+      </c>
+      <c r="F103" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="103" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C103" s="2" t="s">
+    <row r="104" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C104" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="D103" t="s">
-        <v>204</v>
-      </c>
-      <c r="E103" t="s">
-        <v>1</v>
-      </c>
-      <c r="F103" t="s">
+      <c r="D104" t="s">
+        <v>204</v>
+      </c>
+      <c r="E104" t="s">
+        <v>1</v>
+      </c>
+      <c r="F104" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="104" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C104" s="2" t="s">
+    <row r="105" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C105" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="D104" t="s">
-        <v>204</v>
-      </c>
-      <c r="E104" t="s">
-        <v>1</v>
-      </c>
-      <c r="F104" t="s">
+      <c r="D105" t="s">
+        <v>204</v>
+      </c>
+      <c r="E105" t="s">
+        <v>1</v>
+      </c>
+      <c r="F105" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="105" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C105" s="2" t="s">
+    <row r="106" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C106" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="D105" t="s">
-        <v>204</v>
-      </c>
-      <c r="E105" t="s">
-        <v>1</v>
-      </c>
-      <c r="F105" t="s">
+      <c r="D106" t="s">
+        <v>204</v>
+      </c>
+      <c r="E106" t="s">
+        <v>1</v>
+      </c>
+      <c r="F106" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="106" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C106" s="2" t="s">
+    <row r="107" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C107" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="D106" t="s">
-        <v>204</v>
-      </c>
-      <c r="E106" t="s">
-        <v>1</v>
-      </c>
-      <c r="F106" t="s">
+      <c r="D107" t="s">
+        <v>204</v>
+      </c>
+      <c r="E107" t="s">
+        <v>1</v>
+      </c>
+      <c r="F107" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="107" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C107" s="2" t="s">
+    <row r="108" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C108" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="D107" t="s">
-        <v>204</v>
-      </c>
-      <c r="E107" t="s">
-        <v>1</v>
-      </c>
-      <c r="F107" t="s">
+      <c r="D108" t="s">
+        <v>204</v>
+      </c>
+      <c r="E108" t="s">
+        <v>1</v>
+      </c>
+      <c r="F108" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="108" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C108" s="2" t="s">
+    <row r="109" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C109" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="D108" t="s">
-        <v>204</v>
-      </c>
-      <c r="E108" t="s">
-        <v>1</v>
-      </c>
-      <c r="F108" t="s">
+      <c r="D109" t="s">
+        <v>204</v>
+      </c>
+      <c r="E109" t="s">
+        <v>1</v>
+      </c>
+      <c r="F109" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="109" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C109" s="2" t="s">
+    <row r="110" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C110" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="D109" t="s">
-        <v>204</v>
-      </c>
-      <c r="E109" t="s">
-        <v>1</v>
-      </c>
-      <c r="F109" t="s">
+      <c r="D110" t="s">
+        <v>204</v>
+      </c>
+      <c r="E110" t="s">
+        <v>1</v>
+      </c>
+      <c r="F110" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="110" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C110" s="2" t="s">
+    <row r="111" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C111" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="D110" t="s">
-        <v>204</v>
-      </c>
-      <c r="E110" t="s">
-        <v>1</v>
-      </c>
-      <c r="F110" t="s">
+      <c r="D111" t="s">
+        <v>204</v>
+      </c>
+      <c r="E111" t="s">
+        <v>1</v>
+      </c>
+      <c r="F111" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="111" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C111" s="2" t="s">
+    <row r="112" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C112" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="D111" t="s">
-        <v>204</v>
-      </c>
-      <c r="E111" t="s">
-        <v>1</v>
-      </c>
-      <c r="F111" t="s">
+      <c r="D112" t="s">
+        <v>204</v>
+      </c>
+      <c r="E112" t="s">
+        <v>1</v>
+      </c>
+      <c r="F112" t="s">
         <v>304</v>
-      </c>
-    </row>
-    <row r="112" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C112" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="D112" t="s">
-        <v>204</v>
-      </c>
-      <c r="E112" t="s">
-        <v>1</v>
-      </c>
-      <c r="F112" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C113" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D113" t="s">
         <v>204</v>
@@ -3912,12 +3918,12 @@
         <v>1</v>
       </c>
       <c r="F113" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C114" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D114" t="s">
         <v>204</v>
@@ -3926,12 +3932,12 @@
         <v>1</v>
       </c>
       <c r="F114" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C115" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D115" t="s">
         <v>204</v>
@@ -3940,12 +3946,12 @@
         <v>1</v>
       </c>
       <c r="F115" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C116" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D116" t="s">
         <v>204</v>
@@ -3954,12 +3960,12 @@
         <v>1</v>
       </c>
       <c r="F116" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C117" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D117" t="s">
         <v>204</v>
@@ -3968,12 +3974,12 @@
         <v>1</v>
       </c>
       <c r="F117" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C118" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D118" t="s">
         <v>204</v>
@@ -3982,12 +3988,12 @@
         <v>1</v>
       </c>
       <c r="F118" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C119" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D119" t="s">
         <v>204</v>
@@ -3996,12 +4002,12 @@
         <v>1</v>
       </c>
       <c r="F119" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C120" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D120" t="s">
         <v>204</v>
@@ -4010,12 +4016,12 @@
         <v>1</v>
       </c>
       <c r="F120" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C121" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D121" t="s">
         <v>204</v>
@@ -4024,12 +4030,12 @@
         <v>1</v>
       </c>
       <c r="F121" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C122" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D122" t="s">
         <v>204</v>
@@ -4038,12 +4044,12 @@
         <v>1</v>
       </c>
       <c r="F122" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C123" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D123" t="s">
         <v>204</v>
@@ -4052,12 +4058,12 @@
         <v>1</v>
       </c>
       <c r="F123" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C124" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D124" t="s">
         <v>204</v>
@@ -4066,60 +4072,60 @@
         <v>1</v>
       </c>
       <c r="F124" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C125" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D125" t="s">
+        <v>204</v>
+      </c>
+      <c r="E125" t="s">
+        <v>1</v>
+      </c>
+      <c r="F125" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C126" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D125" t="s">
-        <v>204</v>
-      </c>
-      <c r="E125" t="s">
-        <v>1</v>
-      </c>
-      <c r="F125" t="s">
+      <c r="D126" t="s">
+        <v>204</v>
+      </c>
+      <c r="E126" t="s">
+        <v>1</v>
+      </c>
+      <c r="F126" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="126" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="3" t="s">
+    <row r="127" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B126" s="3" t="s">
+      <c r="B127" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="C126" s="2" t="s">
+      <c r="C127" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="D126" t="s">
-        <v>204</v>
-      </c>
-      <c r="E126" t="s">
-        <v>1</v>
-      </c>
-      <c r="F126" t="s">
+      <c r="D127" t="s">
+        <v>204</v>
+      </c>
+      <c r="E127" t="s">
+        <v>1</v>
+      </c>
+      <c r="F127" t="s">
         <v>273</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C127" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D127" t="s">
-        <v>204</v>
-      </c>
-      <c r="E127" t="s">
-        <v>1</v>
-      </c>
-      <c r="F127" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C128" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D128" t="s">
         <v>204</v>
@@ -4128,12 +4134,12 @@
         <v>1</v>
       </c>
       <c r="F128" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="129" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C129" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D129" t="s">
         <v>204</v>
@@ -4142,12 +4148,12 @@
         <v>1</v>
       </c>
       <c r="F129" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="130" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C130" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D130" t="s">
         <v>204</v>
@@ -4156,12 +4162,12 @@
         <v>1</v>
       </c>
       <c r="F130" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="131" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C131" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D131" t="s">
         <v>204</v>
@@ -4170,12 +4176,12 @@
         <v>1</v>
       </c>
       <c r="F131" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="132" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C132" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D132" t="s">
         <v>204</v>
@@ -4184,12 +4190,12 @@
         <v>1</v>
       </c>
       <c r="F132" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="133" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C133" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D133" t="s">
         <v>204</v>
@@ -4198,12 +4204,12 @@
         <v>1</v>
       </c>
       <c r="F133" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="134" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C134" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D134" t="s">
         <v>204</v>
@@ -4212,12 +4218,12 @@
         <v>1</v>
       </c>
       <c r="F134" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="135" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C135" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D135" t="s">
         <v>204</v>
@@ -4226,12 +4232,12 @@
         <v>1</v>
       </c>
       <c r="F135" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="136" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C136" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D136" t="s">
         <v>204</v>
@@ -4240,12 +4246,12 @@
         <v>1</v>
       </c>
       <c r="F136" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="137" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C137" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D137" t="s">
         <v>204</v>
@@ -4254,12 +4260,12 @@
         <v>1</v>
       </c>
       <c r="F137" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="138" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C138" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D138" t="s">
         <v>204</v>
@@ -4268,12 +4274,12 @@
         <v>1</v>
       </c>
       <c r="F138" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="139" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C139" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D139" t="s">
         <v>204</v>
@@ -4282,12 +4288,12 @@
         <v>1</v>
       </c>
       <c r="F139" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="140" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C140" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D140" t="s">
         <v>204</v>
@@ -4296,12 +4302,12 @@
         <v>1</v>
       </c>
       <c r="F140" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="141" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C141" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D141" t="s">
         <v>204</v>
@@ -4310,12 +4316,12 @@
         <v>1</v>
       </c>
       <c r="F141" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="142" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C142" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D142" t="s">
         <v>204</v>
@@ -4324,12 +4330,12 @@
         <v>1</v>
       </c>
       <c r="F142" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="143" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C143" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D143" t="s">
         <v>204</v>
@@ -4338,12 +4344,12 @@
         <v>1</v>
       </c>
       <c r="F143" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="144" spans="3:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C144" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D144" t="s">
         <v>204</v>
@@ -4352,452 +4358,452 @@
         <v>1</v>
       </c>
       <c r="F144" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="145" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C145" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D145" t="s">
+        <v>204</v>
+      </c>
+      <c r="E145" t="s">
+        <v>1</v>
+      </c>
+      <c r="F145" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C146" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="D145" t="s">
-        <v>204</v>
-      </c>
-      <c r="E145" t="s">
-        <v>1</v>
-      </c>
-      <c r="F145" t="s">
+      <c r="D146" t="s">
+        <v>204</v>
+      </c>
+      <c r="E146" t="s">
+        <v>1</v>
+      </c>
+      <c r="F146" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="146" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="3" t="s">
+    <row r="147" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B146" s="3" t="s">
+      <c r="B147" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C147" t="s">
         <v>233</v>
       </c>
-      <c r="D146" t="s">
-        <v>204</v>
-      </c>
-      <c r="F146" t="s">
+      <c r="D147" t="s">
+        <v>204</v>
+      </c>
+      <c r="F147" t="s">
         <v>232</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C147" t="s">
-        <v>231</v>
-      </c>
-      <c r="D147" t="s">
-        <v>204</v>
-      </c>
-      <c r="F147" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C148" t="s">
+        <v>231</v>
+      </c>
+      <c r="D148" t="s">
+        <v>204</v>
+      </c>
+      <c r="F148" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C149" t="s">
         <v>229</v>
       </c>
-      <c r="D148" t="s">
-        <v>204</v>
-      </c>
-      <c r="F148" t="s">
+      <c r="D149" t="s">
+        <v>204</v>
+      </c>
+      <c r="F149" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="149" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="3" t="s">
+    <row r="150" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B149" s="3" t="s">
+      <c r="B150" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C149" t="s">
+      <c r="C150" t="s">
         <v>226</v>
       </c>
-      <c r="D149" t="s">
-        <v>204</v>
-      </c>
-      <c r="F149" t="s">
+      <c r="D150" t="s">
+        <v>204</v>
+      </c>
+      <c r="F150" t="s">
         <v>225</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C150" t="s">
-        <v>224</v>
-      </c>
-      <c r="D150" t="s">
-        <v>204</v>
-      </c>
-      <c r="F150" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C151" t="s">
+        <v>224</v>
+      </c>
+      <c r="D151" t="s">
+        <v>204</v>
+      </c>
+      <c r="F151" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C152" t="s">
         <v>222</v>
       </c>
-      <c r="D151" t="s">
-        <v>204</v>
-      </c>
-      <c r="F151" t="s">
+      <c r="D152" t="s">
+        <v>204</v>
+      </c>
+      <c r="F152" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="152" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="3" t="s">
+    <row r="153" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B152" s="3" t="s">
+      <c r="B153" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C152" s="2" t="s">
+      <c r="C153" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="D152" t="s">
-        <v>204</v>
-      </c>
-      <c r="F152" t="s">
+      <c r="D153" t="s">
+        <v>204</v>
+      </c>
+      <c r="F153" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="153" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C153" s="2" t="s">
+    <row r="154" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C154" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="D153" t="s">
-        <v>204</v>
-      </c>
-      <c r="F153" t="s">
+      <c r="D154" t="s">
+        <v>204</v>
+      </c>
+      <c r="F154" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="154" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="3" t="s">
+    <row r="155" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A155" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B154" s="3" t="s">
+      <c r="B155" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C154" t="s">
+      <c r="C155" t="s">
         <v>218</v>
       </c>
-      <c r="D154" t="s">
-        <v>204</v>
-      </c>
-      <c r="F154" t="s">
+      <c r="D155" t="s">
+        <v>204</v>
+      </c>
+      <c r="F155" t="s">
         <v>217</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C155" t="s">
-        <v>216</v>
-      </c>
-      <c r="D155" t="s">
-        <v>204</v>
-      </c>
-      <c r="F155" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="156" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C156" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D156" t="s">
         <v>204</v>
       </c>
       <c r="F156" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="157" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C157" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D157" t="s">
         <v>204</v>
       </c>
       <c r="F157" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C158" t="s">
+        <v>212</v>
+      </c>
+      <c r="D158" t="s">
+        <v>204</v>
+      </c>
+      <c r="F158" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C159" t="s">
         <v>210</v>
       </c>
-      <c r="D158" t="s">
-        <v>204</v>
-      </c>
-      <c r="F158" t="s">
+      <c r="D159" t="s">
+        <v>204</v>
+      </c>
+      <c r="F159" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="159" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="3" t="s">
+    <row r="160" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B159" s="3" t="s">
+      <c r="B160" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C159" t="s">
+      <c r="C160" t="s">
         <v>207</v>
       </c>
-      <c r="D159" t="s">
-        <v>204</v>
-      </c>
-      <c r="F159" t="s">
+      <c r="D160" t="s">
+        <v>204</v>
+      </c>
+      <c r="F160" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="160" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C160" t="s">
+    <row r="161" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C161" t="s">
         <v>205</v>
       </c>
-      <c r="D160" t="s">
-        <v>204</v>
-      </c>
-      <c r="F160" t="s">
+      <c r="D161" t="s">
+        <v>204</v>
+      </c>
+      <c r="F161" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="161" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="3" t="s">
+    <row r="162" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A162" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B161" s="3" t="s">
+      <c r="B162" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C161" s="2" t="s">
+      <c r="C162" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="D161" t="s">
-        <v>9</v>
-      </c>
-      <c r="E161" t="s">
-        <v>2</v>
-      </c>
-      <c r="F161" t="s">
+      <c r="D162" t="s">
+        <v>9</v>
+      </c>
+      <c r="E162" t="s">
+        <v>2</v>
+      </c>
+      <c r="F162" t="s">
         <v>201</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C162" t="s">
-        <v>200</v>
-      </c>
-      <c r="D162" t="s">
-        <v>9</v>
-      </c>
-      <c r="F162" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="163" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C163" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D163" t="s">
         <v>9</v>
       </c>
       <c r="F163" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="164" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C164" t="s">
+        <v>198</v>
+      </c>
+      <c r="D164" t="s">
+        <v>9</v>
+      </c>
+      <c r="F164" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C165" t="s">
         <v>196</v>
       </c>
-      <c r="D164" t="s">
-        <v>9</v>
-      </c>
-      <c r="F164" t="s">
+      <c r="D165" t="s">
+        <v>9</v>
+      </c>
+      <c r="F165" t="s">
         <v>195</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C165" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="D165" t="s">
-        <v>9</v>
-      </c>
-      <c r="E165" t="s">
-        <v>2</v>
-      </c>
-      <c r="F165" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="166" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C166" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D166" t="s">
+        <v>9</v>
+      </c>
+      <c r="E166" t="s">
+        <v>2</v>
+      </c>
+      <c r="F166" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C167" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D166" t="s">
-        <v>9</v>
-      </c>
-      <c r="E166" t="s">
-        <v>2</v>
-      </c>
-      <c r="F166" t="s">
+      <c r="D167" t="s">
+        <v>9</v>
+      </c>
+      <c r="E167" t="s">
+        <v>2</v>
+      </c>
+      <c r="F167" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="167" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C167" t="s">
+    <row r="168" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C168" t="s">
         <v>190</v>
       </c>
-      <c r="D167" t="s">
-        <v>9</v>
-      </c>
-      <c r="F167" t="s">
+      <c r="D168" t="s">
+        <v>9</v>
+      </c>
+      <c r="F168" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="168" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="3" t="s">
+    <row r="169" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A169" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B168" s="3" t="s">
+      <c r="B169" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C168" t="s">
+      <c r="C169" t="s">
         <v>187</v>
       </c>
-      <c r="D168" t="s">
-        <v>9</v>
-      </c>
-      <c r="F168" t="s">
+      <c r="D169" t="s">
+        <v>9</v>
+      </c>
+      <c r="F169" t="s">
         <v>186</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C169" t="s">
-        <v>185</v>
-      </c>
-      <c r="D169" t="s">
-        <v>9</v>
-      </c>
-      <c r="F169" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="170" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C170" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D170" t="s">
         <v>9</v>
       </c>
       <c r="F170" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="171" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C171" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D171" t="s">
         <v>9</v>
       </c>
       <c r="F171" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C172" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D172" t="s">
         <v>9</v>
       </c>
       <c r="F172" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="173" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C173" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D173" t="s">
         <v>9</v>
       </c>
       <c r="F173" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="174" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C174" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D174" t="s">
         <v>9</v>
       </c>
       <c r="F174" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="175" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C175" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D175" t="s">
         <v>9</v>
       </c>
       <c r="F175" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="176" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C176" t="s">
+        <v>173</v>
+      </c>
+      <c r="D176" t="s">
+        <v>9</v>
+      </c>
+      <c r="F176" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C177" t="s">
         <v>171</v>
       </c>
-      <c r="D176" t="s">
-        <v>9</v>
-      </c>
-      <c r="F176" t="s">
+      <c r="D177" t="s">
+        <v>9</v>
+      </c>
+      <c r="F177" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="3" t="s">
+    <row r="178" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A178" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B177" s="3" t="s">
+      <c r="B178" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C177" s="2" t="s">
+      <c r="C178" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="D177" t="s">
-        <v>9</v>
-      </c>
-      <c r="E177" t="s">
-        <v>2</v>
-      </c>
-      <c r="F177" t="s">
+      <c r="D178" t="s">
+        <v>9</v>
+      </c>
+      <c r="E178" t="s">
+        <v>2</v>
+      </c>
+      <c r="F178" t="s">
         <v>167</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C178" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D178" t="s">
-        <v>9</v>
-      </c>
-      <c r="E178" t="s">
-        <v>2</v>
-      </c>
-      <c r="F178" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="179" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C179" s="2" t="s">
-        <v>164</v>
+        <v>569</v>
       </c>
       <c r="D179" t="s">
         <v>9</v>
@@ -4806,12 +4812,12 @@
         <v>2</v>
       </c>
       <c r="F179" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="180" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C180" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D180" t="s">
         <v>9</v>
@@ -4820,12 +4826,12 @@
         <v>2</v>
       </c>
       <c r="F180" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="181" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C181" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D181" t="s">
         <v>9</v>
@@ -4834,12 +4840,12 @@
         <v>2</v>
       </c>
       <c r="F181" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="182" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C182" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D182" t="s">
         <v>9</v>
@@ -4848,46 +4854,46 @@
         <v>2</v>
       </c>
       <c r="F182" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="183" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B183" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="C183" s="2" t="s">
-        <v>563</v>
+        <v>160</v>
       </c>
       <c r="D183" t="s">
         <v>9</v>
       </c>
       <c r="E183" t="s">
-        <v>138</v>
+        <v>2</v>
       </c>
       <c r="F183" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="184" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C184" s="2" t="s">
-        <v>564</v>
+        <v>158</v>
       </c>
       <c r="D184" t="s">
         <v>9</v>
       </c>
       <c r="E184" t="s">
-        <v>138</v>
+        <v>2</v>
       </c>
       <c r="F184" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="185" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A185" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>156</v>
+      </c>
       <c r="C185" s="2" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="D185" t="s">
         <v>9</v>
@@ -4896,12 +4902,12 @@
         <v>138</v>
       </c>
       <c r="F185" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="186" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C186" s="2" t="s">
-        <v>152</v>
+        <v>564</v>
       </c>
       <c r="D186" t="s">
         <v>9</v>
@@ -4910,18 +4916,12 @@
         <v>138</v>
       </c>
       <c r="F186" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="187" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B187" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="C187" s="2" t="s">
-        <v>149</v>
+        <v>565</v>
       </c>
       <c r="D187" t="s">
         <v>9</v>
@@ -4930,12 +4930,12 @@
         <v>138</v>
       </c>
       <c r="F187" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C188" s="2" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D188" t="s">
         <v>9</v>
@@ -4944,12 +4944,18 @@
         <v>138</v>
       </c>
       <c r="F188" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="189" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>150</v>
+      </c>
       <c r="C189" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D189" t="s">
         <v>9</v>
@@ -4958,12 +4964,12 @@
         <v>138</v>
       </c>
       <c r="F189" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="190" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C190" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D190" t="s">
         <v>9</v>
@@ -4972,12 +4978,12 @@
         <v>138</v>
       </c>
       <c r="F190" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C191" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D191" t="s">
         <v>9</v>
@@ -4986,12 +4992,12 @@
         <v>138</v>
       </c>
       <c r="F191" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="192" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C192" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D192" t="s">
         <v>9</v>
@@ -5000,331 +5006,331 @@
         <v>138</v>
       </c>
       <c r="F192" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C193" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D193" t="s">
+        <v>9</v>
+      </c>
+      <c r="E193" t="s">
+        <v>138</v>
+      </c>
+      <c r="F193" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C194" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D194" t="s">
+        <v>9</v>
+      </c>
+      <c r="E194" t="s">
+        <v>138</v>
+      </c>
+      <c r="F194" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="193" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C193" t="s">
+    <row r="195" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C195" t="s">
         <v>136</v>
       </c>
-      <c r="D193" t="s">
-        <v>9</v>
-      </c>
-      <c r="F193" t="s">
+      <c r="D195" t="s">
+        <v>9</v>
+      </c>
+      <c r="F195" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="194" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C194" t="s">
+    <row r="196" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C196" t="s">
         <v>134</v>
       </c>
-      <c r="D194" t="s">
-        <v>9</v>
-      </c>
-      <c r="F194" t="s">
+      <c r="D196" t="s">
+        <v>9</v>
+      </c>
+      <c r="F196" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="195" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="3" t="s">
+    <row r="197" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A197" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B195" s="3" t="s">
+      <c r="B197" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C195" s="2" t="s">
+      <c r="C197" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D195" t="s">
-        <v>9</v>
-      </c>
-      <c r="F195" t="s">
+      <c r="D197" t="s">
+        <v>9</v>
+      </c>
+      <c r="F197" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="196" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C196" s="2" t="s">
+    <row r="198" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C198" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D196" t="s">
-        <v>9</v>
-      </c>
-      <c r="F196" t="s">
+      <c r="D198" t="s">
+        <v>9</v>
+      </c>
+      <c r="F198" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="197" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C197" s="2" t="s">
+    <row r="199" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C199" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D197" t="s">
-        <v>9</v>
-      </c>
-      <c r="F197" t="s">
+      <c r="D199" t="s">
+        <v>9</v>
+      </c>
+      <c r="F199" t="s">
         <v>126</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C198" t="s">
-        <v>125</v>
-      </c>
-      <c r="D198" t="s">
-        <v>9</v>
-      </c>
-      <c r="F198" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C199" t="s">
-        <v>123</v>
-      </c>
-      <c r="D199" t="s">
-        <v>9</v>
-      </c>
-      <c r="F199" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="200" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C200" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D200" t="s">
         <v>9</v>
       </c>
       <c r="F200" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="201" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C201" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D201" t="s">
         <v>9</v>
       </c>
       <c r="F201" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="202" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C202" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D202" t="s">
         <v>9</v>
       </c>
       <c r="F202" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="203" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C203" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D203" t="s">
         <v>9</v>
       </c>
       <c r="F203" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="204" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C204" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D204" t="s">
         <v>9</v>
       </c>
       <c r="F204" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="205" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C205" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D205" t="s">
         <v>9</v>
       </c>
       <c r="F205" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="206" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A206" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B206" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="C206" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D206" t="s">
         <v>9</v>
       </c>
       <c r="F206" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="207" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C207" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D207" t="s">
         <v>9</v>
       </c>
       <c r="F207" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A208" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>109</v>
+      </c>
       <c r="C208" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D208" t="s">
         <v>9</v>
       </c>
       <c r="F208" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="209" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C209" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D209" t="s">
         <v>9</v>
       </c>
       <c r="F209" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="210" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C210" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D210" t="s">
         <v>9</v>
       </c>
       <c r="F210" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="211" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C211" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D211" t="s">
         <v>9</v>
       </c>
       <c r="F211" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="212" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C212" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D212" t="s">
         <v>9</v>
       </c>
       <c r="F212" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="213" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C213" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D213" t="s">
         <v>9</v>
       </c>
       <c r="F213" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="214" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A214" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B214" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="C214" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D214" t="s">
         <v>9</v>
       </c>
       <c r="F214" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="215" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C215" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D215" t="s">
         <v>9</v>
       </c>
       <c r="F215" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="216" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C216" t="s">
+        <v>91</v>
+      </c>
+      <c r="D216" t="s">
+        <v>9</v>
+      </c>
+      <c r="F216" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C217" t="s">
+        <v>89</v>
+      </c>
+      <c r="D217" t="s">
+        <v>9</v>
+      </c>
+      <c r="F217" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A218" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B216" s="3" t="s">
+      <c r="B218" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C216" s="2" t="s">
+      <c r="C218" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D216" t="s">
-        <v>9</v>
-      </c>
-      <c r="E216" t="s">
-        <v>2</v>
-      </c>
-      <c r="F216" t="s">
+      <c r="D218" t="s">
+        <v>9</v>
+      </c>
+      <c r="E218" t="s">
+        <v>2</v>
+      </c>
+      <c r="F218" t="s">
         <v>85</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C217" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D217" t="s">
-        <v>9</v>
-      </c>
-      <c r="E217" t="s">
-        <v>2</v>
-      </c>
-      <c r="F217" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C218" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D218" t="s">
-        <v>9</v>
-      </c>
-      <c r="E218" t="s">
-        <v>2</v>
-      </c>
-      <c r="F218" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="219" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C219" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D219" t="s">
         <v>9</v>
@@ -5333,12 +5339,12 @@
         <v>2</v>
       </c>
       <c r="F219" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="220" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C220" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D220" t="s">
         <v>9</v>
@@ -5347,12 +5353,12 @@
         <v>2</v>
       </c>
       <c r="F220" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="221" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C221" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D221" t="s">
         <v>9</v>
@@ -5361,12 +5367,12 @@
         <v>2</v>
       </c>
       <c r="F221" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="222" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C222" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D222" t="s">
         <v>9</v>
@@ -5375,12 +5381,12 @@
         <v>2</v>
       </c>
       <c r="F222" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="223" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C223" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D223" t="s">
         <v>9</v>
@@ -5389,12 +5395,12 @@
         <v>2</v>
       </c>
       <c r="F223" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="224" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C224" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D224" t="s">
         <v>9</v>
@@ -5403,12 +5409,12 @@
         <v>2</v>
       </c>
       <c r="F224" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="225" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C225" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D225" t="s">
         <v>9</v>
@@ -5417,12 +5423,12 @@
         <v>2</v>
       </c>
       <c r="F225" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="226" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C226" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D226" t="s">
         <v>9</v>
@@ -5431,12 +5437,12 @@
         <v>2</v>
       </c>
       <c r="F226" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="227" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C227" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D227" t="s">
         <v>9</v>
@@ -5445,12 +5451,12 @@
         <v>2</v>
       </c>
       <c r="F227" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="228" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C228" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D228" t="s">
         <v>9</v>
@@ -5459,12 +5465,12 @@
         <v>2</v>
       </c>
       <c r="F228" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="229" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C229" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D229" t="s">
         <v>9</v>
@@ -5473,12 +5479,12 @@
         <v>2</v>
       </c>
       <c r="F229" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="230" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C230" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D230" t="s">
         <v>9</v>
@@ -5487,12 +5493,12 @@
         <v>2</v>
       </c>
       <c r="F230" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="231" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C231" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D231" t="s">
         <v>9</v>
@@ -5501,18 +5507,12 @@
         <v>2</v>
       </c>
       <c r="F231" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="232" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A232" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B232" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="C232" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D232" t="s">
         <v>9</v>
@@ -5521,12 +5521,12 @@
         <v>2</v>
       </c>
       <c r="F232" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="233" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C233" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D233" t="s">
         <v>9</v>
@@ -5535,12 +5535,18 @@
         <v>2</v>
       </c>
       <c r="F233" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="234" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A234" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="C234" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D234" t="s">
         <v>9</v>
@@ -5549,12 +5555,12 @@
         <v>2</v>
       </c>
       <c r="F234" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="235" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C235" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D235" t="s">
         <v>9</v>
@@ -5563,12 +5569,12 @@
         <v>2</v>
       </c>
       <c r="F235" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="236" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C236" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D236" t="s">
         <v>9</v>
@@ -5577,12 +5583,12 @@
         <v>2</v>
       </c>
       <c r="F236" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="237" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C237" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D237" t="s">
         <v>9</v>
@@ -5591,12 +5597,12 @@
         <v>2</v>
       </c>
       <c r="F237" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="238" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C238" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D238" t="s">
         <v>9</v>
@@ -5605,12 +5611,12 @@
         <v>2</v>
       </c>
       <c r="F238" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="239" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C239" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D239" t="s">
         <v>9</v>
@@ -5619,244 +5625,258 @@
         <v>2</v>
       </c>
       <c r="F239" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="240" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C240" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D240" t="s">
+        <v>9</v>
+      </c>
+      <c r="E240" t="s">
+        <v>2</v>
+      </c>
+      <c r="F240" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C241" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D241" t="s">
+        <v>9</v>
+      </c>
+      <c r="E241" t="s">
+        <v>2</v>
+      </c>
+      <c r="F241" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C242" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D240" t="s">
-        <v>9</v>
-      </c>
-      <c r="E240" t="s">
-        <v>2</v>
-      </c>
-      <c r="F240" t="s">
+      <c r="D242" t="s">
+        <v>9</v>
+      </c>
+      <c r="E242" t="s">
+        <v>2</v>
+      </c>
+      <c r="F242" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="241" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A241" s="3" t="s">
+    <row r="243" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A243" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B241" s="3" t="s">
+      <c r="B243" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C241" s="2" t="s">
+      <c r="C243" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D241" t="s">
-        <v>9</v>
-      </c>
-      <c r="E241" t="s">
-        <v>2</v>
-      </c>
-      <c r="F241" t="s">
+      <c r="D243" t="s">
+        <v>9</v>
+      </c>
+      <c r="E243" t="s">
+        <v>2</v>
+      </c>
+      <c r="F243" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="242" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C242" s="2" t="s">
+    <row r="244" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C244" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D242" t="s">
-        <v>9</v>
-      </c>
-      <c r="E242" t="s">
-        <v>2</v>
-      </c>
-      <c r="F242" t="s">
+      <c r="D244" t="s">
+        <v>9</v>
+      </c>
+      <c r="E244" t="s">
+        <v>2</v>
+      </c>
+      <c r="F244" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="243" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C243" s="2" t="s">
+    <row r="245" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C245" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D243" t="s">
-        <v>9</v>
-      </c>
-      <c r="E243" t="s">
-        <v>2</v>
-      </c>
-      <c r="F243" t="s">
+      <c r="D245" t="s">
+        <v>9</v>
+      </c>
+      <c r="E245" t="s">
+        <v>2</v>
+      </c>
+      <c r="F245" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="244" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C244" s="2" t="s">
+    <row r="246" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C246" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D244" t="s">
-        <v>9</v>
-      </c>
-      <c r="E244" t="s">
-        <v>2</v>
-      </c>
-      <c r="F244" t="s">
+      <c r="D246" t="s">
+        <v>9</v>
+      </c>
+      <c r="E246" t="s">
+        <v>2</v>
+      </c>
+      <c r="F246" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="245" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C245" s="2" t="s">
+    <row r="247" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C247" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D245" t="s">
-        <v>9</v>
-      </c>
-      <c r="E245" t="s">
-        <v>2</v>
-      </c>
-      <c r="F245" t="s">
+      <c r="D247" t="s">
+        <v>9</v>
+      </c>
+      <c r="E247" t="s">
+        <v>2</v>
+      </c>
+      <c r="F247" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="246" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C246" s="2" t="s">
+    <row r="248" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C248" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D246" t="s">
-        <v>9</v>
-      </c>
-      <c r="E246" t="s">
-        <v>2</v>
-      </c>
-      <c r="F246" t="s">
+      <c r="D248" t="s">
+        <v>9</v>
+      </c>
+      <c r="E248" t="s">
+        <v>2</v>
+      </c>
+      <c r="F248" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="247" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C247" s="2" t="s">
+    <row r="249" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C249" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D247" t="s">
-        <v>9</v>
-      </c>
-      <c r="E247" t="s">
-        <v>2</v>
-      </c>
-      <c r="F247" t="s">
+      <c r="D249" t="s">
+        <v>9</v>
+      </c>
+      <c r="E249" t="s">
+        <v>2</v>
+      </c>
+      <c r="F249" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="248" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C248" s="2" t="s">
+    <row r="250" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C250" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D248" t="s">
-        <v>9</v>
-      </c>
-      <c r="E248" t="s">
-        <v>2</v>
-      </c>
-      <c r="F248" t="s">
+      <c r="D250" t="s">
+        <v>9</v>
+      </c>
+      <c r="E250" t="s">
+        <v>2</v>
+      </c>
+      <c r="F250" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="249" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C249" s="2" t="s">
+    <row r="251" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C251" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D249" t="s">
-        <v>9</v>
-      </c>
-      <c r="E249" t="s">
-        <v>2</v>
-      </c>
-      <c r="F249" t="s">
+      <c r="D251" t="s">
+        <v>9</v>
+      </c>
+      <c r="E251" t="s">
+        <v>2</v>
+      </c>
+      <c r="F251" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="250" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C250" s="2" t="s">
+    <row r="252" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C252" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D250" t="s">
-        <v>9</v>
-      </c>
-      <c r="E250" t="s">
-        <v>2</v>
-      </c>
-      <c r="F250" t="s">
+      <c r="D252" t="s">
+        <v>9</v>
+      </c>
+      <c r="E252" t="s">
+        <v>2</v>
+      </c>
+      <c r="F252" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="251" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C251" s="2" t="s">
+    <row r="253" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C253" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D251" t="s">
-        <v>9</v>
-      </c>
-      <c r="E251" t="s">
-        <v>2</v>
-      </c>
-      <c r="F251" t="s">
+      <c r="D253" t="s">
+        <v>9</v>
+      </c>
+      <c r="E253" t="s">
+        <v>2</v>
+      </c>
+      <c r="F253" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="252" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C252" s="2" t="s">
+    <row r="254" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C254" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D252" t="s">
-        <v>9</v>
-      </c>
-      <c r="E252" t="s">
-        <v>2</v>
-      </c>
-      <c r="F252" t="s">
+      <c r="D254" t="s">
+        <v>9</v>
+      </c>
+      <c r="E254" t="s">
+        <v>2</v>
+      </c>
+      <c r="F254" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="253" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A253" s="3" t="s">
+    <row r="255" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A255" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B253" s="3" t="s">
+      <c r="B255" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C253" s="2" t="s">
+      <c r="C255" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D253" t="s">
-        <v>2</v>
-      </c>
-      <c r="E253" t="s">
-        <v>1</v>
-      </c>
-      <c r="F253" t="s">
+      <c r="D255" t="s">
+        <v>2</v>
+      </c>
+      <c r="E255" t="s">
+        <v>1</v>
+      </c>
+      <c r="F255" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="254" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C254" s="2" t="s">
+    <row r="256" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C256" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D254" t="s">
-        <v>2</v>
-      </c>
-      <c r="E254" t="s">
-        <v>1</v>
-      </c>
-      <c r="F254" t="s">
+      <c r="D256" t="s">
+        <v>2</v>
+      </c>
+      <c r="E256" t="s">
+        <v>1</v>
+      </c>
+      <c r="F256" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="255" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C255" s="1"/>
-      <c r="D255" s="1"/>
-      <c r="E255" s="1"/>
-      <c r="F255" s="1"/>
-      <c r="G255" s="1"/>
-    </row>
-    <row r="256" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C256" s="1"/>
-      <c r="D256" s="1"/>
-      <c r="E256" s="1"/>
-      <c r="F256" s="1"/>
-      <c r="G256" s="1"/>
     </row>
     <row r="257" spans="3:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C257" s="1"/>
@@ -5949,6 +5969,20 @@
       <c r="F269" s="1"/>
       <c r="G269" s="1"/>
     </row>
+    <row r="270" spans="3:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C270" s="1"/>
+      <c r="D270" s="1"/>
+      <c r="E270" s="1"/>
+      <c r="F270" s="1"/>
+      <c r="G270" s="1"/>
+    </row>
+    <row r="271" spans="3:7" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C271" s="1"/>
+      <c r="D271" s="1"/>
+      <c r="E271" s="1"/>
+      <c r="F271" s="1"/>
+      <c r="G271" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
